--- a/Stats Sheet/Round Gaps/LightningBolt.xlsx
+++ b/Stats Sheet/Round Gaps/LightningBolt.xlsx
@@ -193,9 +193,6 @@
     <x:t>242</x:t>
   </x:si>
   <x:si>
-    <x:t>MojangSupport</x:t>
-  </x:si>
-  <x:si>
     <x:t>NetherrRush</x:t>
   </x:si>
   <x:si>
@@ -209,6 +206,9 @@
   </x:si>
   <x:si>
     <x:t>Topdog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrentxS</x:t>
   </x:si>
   <x:si>
     <x:t>Xeru__</x:t>
@@ -1632,9 +1632,12 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J51" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -1649,12 +1652,9 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I52" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J52" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
